--- a/artfynd/A 63101-2025 artfynd.xlsx
+++ b/artfynd/A 63101-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84981912</v>
+        <v>84981914</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603460.3338587919</v>
+        <v>603501</v>
       </c>
       <c r="R2" t="n">
-        <v>6503781.619348494</v>
+        <v>6503775</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>84981913</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603460.3338587919</v>
+        <v>603460</v>
       </c>
       <c r="R3" t="n">
-        <v>6503781.619348494</v>
+        <v>6503782</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +844,9 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84981914</v>
+        <v>84981912</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603500.6612892295</v>
+        <v>603460</v>
       </c>
       <c r="R4" t="n">
-        <v>6503774.885205402</v>
+        <v>6503782</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,19 +945,9 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +981,7 @@
         <v>84981915</v>
       </c>
       <c r="B5" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603500.6612892295</v>
+        <v>603501</v>
       </c>
       <c r="R5" t="n">
-        <v>6503774.885205402</v>
+        <v>6503775</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,19 +1046,9 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1072,107 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>84981974</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lilla Bötet, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>603340</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6503701</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-10-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Kryptogamer i Södermanlands län</t>
         </is>

--- a/artfynd/A 63101-2025 artfynd.xlsx
+++ b/artfynd/A 63101-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84981914</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84981913</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84981912</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84981915</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84981974</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>